--- a/data/pupil/3_processed/15_semantic_similarity/event/sub_1031_cosine_similarity.xlsx
+++ b/data/pupil/3_processed/15_semantic_similarity/event/sub_1031_cosine_similarity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,10 +451,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Grandfather Clocks</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Impatient Billionaire</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Dont Look</t>
         </is>
@@ -474,9 +479,12 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.8099008798599243</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.4464801549911499</v>
       </c>
     </row>
@@ -494,9 +502,12 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.3923699259757996</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.4295532703399658</v>
       </c>
     </row>
@@ -517,6 +528,9 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.3816876411437988</v>
       </c>
     </row>
@@ -534,9 +548,12 @@
         <v>0.4642889499664307</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.479575127363205</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.520580530166626</v>
       </c>
     </row>
@@ -554,9 +571,12 @@
         <v>0.5576554536819458</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.5884567499160767</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.3858510851860046</v>
       </c>
     </row>
@@ -577,6 +597,9 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.4199191331863403</v>
       </c>
     </row>
@@ -594,9 +617,12 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>0.3697564899921417</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>0.3777694404125214</v>
       </c>
     </row>
@@ -614,9 +640,12 @@
         <v>0.5980661511421204</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.5404118299484253</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>0.4132797718048096</v>
       </c>
     </row>
@@ -634,9 +663,12 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.6102252006530762</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -654,9 +686,12 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.5682664513587952</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -679,6 +714,9 @@
       <c r="F12" t="n">
         <v>0</v>
       </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -694,9 +732,12 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
         <v>0.7222433686256409</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -719,6 +760,9 @@
       <c r="F14" t="n">
         <v>0</v>
       </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -734,9 +778,12 @@
         <v>0.3786589503288269</v>
       </c>
       <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>0.5333663821220398</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>0.4280245006084442</v>
       </c>
     </row>
@@ -754,9 +801,12 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>0.6433793306350708</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>0.3729015290737152</v>
       </c>
     </row>
@@ -774,9 +824,12 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
         <v>0.3735232055187225</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>0.4547983407974243</v>
       </c>
     </row>
@@ -794,9 +847,12 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.5901879072189331</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>0.4591763317584991</v>
       </c>
     </row>
@@ -813,8 +869,11 @@
       <c r="D19" t="n">
         <v>0.2753373384475708</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -831,8 +890,11 @@
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="n">
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -849,8 +911,11 @@
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="n">
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -865,8 +930,11 @@
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="n">
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -881,8 +949,11 @@
       <c r="D23" t="n">
         <v>0.4869639277458191</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="n">
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -897,8 +968,11 @@
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="n">
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
         <v>0.03338433802127838</v>
       </c>
     </row>
@@ -911,8 +985,11 @@
       <c r="D25" t="n">
         <v>0.5965515375137329</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="n">
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
         <v>0.4295853972434998</v>
       </c>
     </row>
@@ -925,8 +1002,11 @@
       <c r="D26" t="n">
         <v>0.605964183807373</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
         <v>0.4906589686870575</v>
       </c>
     </row>
@@ -939,8 +1019,11 @@
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="n">
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
         <v>0.6334193348884583</v>
       </c>
     </row>
@@ -953,8 +1036,11 @@
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="n">
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -967,8 +1053,11 @@
       <c r="D29" t="n">
         <v>0.5585803985595703</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="n">
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -981,8 +1070,11 @@
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="n">
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
         <v>0.1425569504499435</v>
       </c>
     </row>
@@ -996,7 +1088,8 @@
         <v>0</v>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="n">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1010,7 +1103,8 @@
         <v>0</v>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1024,7 +1118,8 @@
         <v>0.4529353976249695</v>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
         <v>0.5355987548828125</v>
       </c>
     </row>
@@ -1038,7 +1133,8 @@
         <v>0.2685833871364594</v>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="n">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
         <v>0.6662301421165466</v>
       </c>
     </row>
@@ -1052,7 +1148,8 @@
         <v>0</v>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="n">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
         <v>0.7225434184074402</v>
       </c>
     </row>
@@ -1066,7 +1163,8 @@
         <v>0.6354278922080994</v>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="n">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
         <v>0.2920913398265839</v>
       </c>
     </row>
@@ -1080,7 +1178,8 @@
         <v>0.4640940427780151</v>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="n">
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
         <v>0.5306137800216675</v>
       </c>
     </row>
@@ -1094,7 +1193,8 @@
         <v>0.2000309824943542</v>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="n">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
         <v>0.1086017414927483</v>
       </c>
     </row>
@@ -1108,7 +1208,8 @@
         <v>0.3720924258232117</v>
       </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="n">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1122,7 +1223,8 @@
         <v>0.4148754179477692</v>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="n">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1136,7 +1238,8 @@
         <v>0.5799391865730286</v>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="n">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
         <v>0.5228120684623718</v>
       </c>
     </row>
@@ -1150,7 +1253,8 @@
         <v>0.4820892214775085</v>
       </c>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="n">
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
         <v>0.2877480685710907</v>
       </c>
     </row>
@@ -1165,6 +1269,7 @@
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1177,6 +1282,7 @@
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1189,6 +1295,7 @@
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1201,6 +1308,7 @@
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1213,6 +1321,7 @@
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1225,6 +1334,7 @@
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1237,6 +1347,7 @@
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1249,6 +1360,7 @@
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1261,6 +1373,7 @@
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1273,6 +1386,7 @@
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1285,6 +1399,7 @@
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1297,6 +1412,7 @@
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1309,6 +1425,7 @@
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1321,6 +1438,7 @@
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
